--- a/station_me.xlsx
+++ b/station_me.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김창보\Desktop\waste way\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김창보\Desktop\waste-way-apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -7270,21 +7270,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -7294,6 +7279,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -7672,13 +7672,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="65" t="s">
         <v>699</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -7688,13 +7688,13 @@
       <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="65" t="s">
         <v>700</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
@@ -7703,16 +7703,16 @@
       <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="72" t="s">
         <v>994</v>
       </c>
-      <c r="D5" s="68"/>
+      <c r="D5" s="72"/>
       <c r="E5" s="47" t="s">
         <v>2112</v>
       </c>
@@ -7721,10 +7721,10 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="67"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
       <c r="E6" s="50"/>
       <c r="F6" s="50"/>
     </row>
@@ -7733,10 +7733,10 @@
       <c r="B7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="67"/>
+      <c r="D7" s="69"/>
       <c r="E7" s="49" t="s">
         <v>2113</v>
       </c>
@@ -7749,10 +7749,10 @@
       <c r="B8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="65"/>
+      <c r="D8" s="70"/>
       <c r="E8" s="48"/>
       <c r="F8" s="53"/>
     </row>
